--- a/券商账户原型业务端到端测试用例.xlsx
+++ b/券商账户原型业务端到端测试用例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925" activeTab="1"/>
+    <workbookView windowWidth="9210" windowHeight="6570" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="开发冒烟测试" sheetId="1" r:id="rId1"/>
@@ -229,6 +229,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -344,6 +349,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>地址证明</t>
     </r>
     <r>
@@ -1554,12 +1564,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1948,7 +1970,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1972,7 +1994,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1996,16 +2018,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2014,145 +2036,157 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2697,302 +2731,302 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:11">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:11">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="22" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" ht="70" customHeight="1" spans="1:11">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="23" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" ht="70" customHeight="1" spans="1:11">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="23" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:11">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="22" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" ht="70" customHeight="1" spans="1:11">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="23" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" ht="70" customHeight="1" spans="1:11">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="23" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:11">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="22" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1" spans="1:11">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="23" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:11">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="22" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="11" ht="70" customHeight="1" spans="1:11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="23" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" ht="70" customHeight="1" spans="1:11">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="23" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3017,1602 +3051,1602 @@
   <dimension ref="A1:I60"/>
   <sheetFormatPr defaultColWidth="21.8571428571429" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="21.8571428571429" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28571428571429" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.8571428571429" style="1" customWidth="1"/>
-    <col min="5" max="5" width="32.5714285714286" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.2857142857143" style="1" customWidth="1"/>
-    <col min="7" max="7" width="48.1428571428571" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.2857142857143" style="1" customWidth="1"/>
-    <col min="9" max="16382" width="21.8571428571429" style="1" customWidth="1"/>
-    <col min="16383" max="16384" width="21.8571428571429" style="1"/>
+    <col min="1" max="2" width="21.8571428571429" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.28571428571429" style="3" customWidth="1"/>
+    <col min="4" max="4" width="21.8571428571429" style="3" customWidth="1"/>
+    <col min="5" max="5" width="32.5714285714286" style="3" customWidth="1"/>
+    <col min="6" max="6" width="37.2857142857143" style="3" customWidth="1"/>
+    <col min="7" max="7" width="48.1428571428571" style="3" customWidth="1"/>
+    <col min="8" max="8" width="34.2857142857143" style="3" customWidth="1"/>
+    <col min="9" max="16382" width="21.8571428571429" style="3" customWidth="1"/>
+    <col min="16383" max="16384" width="21.8571428571429" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:9">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" ht="75" customHeight="1" spans="1:9">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="75" customHeight="1" spans="1:9">
+      <c r="A3" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" ht="70" customHeight="1" spans="1:9">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" ht="70" customHeight="1" spans="1:9">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" ht="70" customHeight="1" spans="1:9">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" ht="70" customHeight="1" spans="1:9">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" ht="70" customHeight="1" spans="1:9">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1" spans="1:9">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" ht="70" customHeight="1" spans="1:9">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" ht="70" customHeight="1" spans="1:9">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:9">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="11" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="13" ht="91" customHeight="1" spans="1:9">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" ht="70" customHeight="1" spans="1:9">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" ht="70" customHeight="1" spans="1:9">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" ht="70" customHeight="1" spans="1:9">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" ht="70" customHeight="1" spans="1:9">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" ht="70" customHeight="1" spans="1:9">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" ht="70" customHeight="1" spans="1:9">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" ht="70" customHeight="1" spans="1:9">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" ht="70" customHeight="1" spans="1:9">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" ht="70" customHeight="1" spans="1:9">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" ht="70" customHeight="1" spans="1:9">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="6" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:9">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="11" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="25" ht="70" customHeight="1" spans="1:9">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" ht="70" customHeight="1" spans="1:9">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="27" ht="70" customHeight="1" spans="1:9">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" ht="70" customHeight="1" spans="1:9">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:9">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="13" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="30" ht="70" customHeight="1" spans="1:9">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I30" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" ht="70" customHeight="1" spans="1:9">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="32" ht="70" customHeight="1" spans="1:9">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" ht="70" customHeight="1" spans="1:9">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="I33" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="34" ht="70" customHeight="1" spans="1:9">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="I34" s="10"/>
+      <c r="I34" s="15"/>
     </row>
     <row r="35" ht="70" customHeight="1" spans="1:9">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="I35" s="10"/>
+      <c r="I35" s="15"/>
     </row>
     <row r="36" ht="70" customHeight="1" spans="1:9">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="I36" s="10"/>
+      <c r="I36" s="15"/>
     </row>
     <row r="37" ht="70" customHeight="1" spans="1:9">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="I37" s="10"/>
+      <c r="I37" s="15"/>
     </row>
     <row r="38" ht="70" customHeight="1" spans="1:9">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="I38" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" ht="70" customHeight="1" spans="1:9">
-      <c r="A39" s="10" t="s">
+      <c r="I38" s="15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" ht="70" customHeight="1" spans="1:9">
+      <c r="A39" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="H39" s="14" t="s">
+      <c r="H39" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I39" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="40" ht="70" customHeight="1" spans="1:9">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="I40" s="10" t="s">
+      <c r="I40" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="41" ht="70" customHeight="1" spans="1:9">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I41" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:9">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="20" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="43" ht="70" customHeight="1" spans="1:9">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="I43" s="10" t="s">
+      <c r="I43" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" ht="70" customHeight="1" spans="1:9">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="I44" s="10" t="s">
+      <c r="I44" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" ht="70" customHeight="1" spans="1:9">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="I45" s="10" t="s">
+      <c r="I45" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" ht="70" customHeight="1" spans="1:9">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="G46" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H46" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="I46" s="10" t="s">
+      <c r="I46" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="47" ht="70" customHeight="1" spans="1:9">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="I47" s="10" t="s">
+      <c r="I47" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="48" ht="70" customHeight="1" spans="1:9">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="E48" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="I48" s="10" t="s">
+      <c r="I48" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" ht="70" customHeight="1" spans="1:9">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="I49" s="10" t="s">
+      <c r="I49" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="50" ht="70" customHeight="1" spans="1:9">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="F50" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H50" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="I50" s="10" t="s">
+      <c r="I50" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="51" ht="70" customHeight="1" spans="1:9">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="I51" s="10" t="s">
+      <c r="I51" s="15" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:9">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="20" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="53" ht="70" customHeight="1" spans="1:9">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="F53" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="I53" s="10" t="s">
+      <c r="I53" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" ht="70" customHeight="1" spans="1:9">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="G54" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="H54" s="10" t="s">
+      <c r="H54" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="I54" s="10" t="s">
+      <c r="I54" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" ht="70" customHeight="1" spans="1:9">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="F55" s="10" t="s">
+      <c r="F55" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="G55" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="I55" s="10" t="s">
+      <c r="I55" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="56" ht="70" customHeight="1" spans="1:9">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="F56" s="10" t="s">
+      <c r="F56" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="G56" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="H56" s="10" t="s">
+      <c r="H56" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="I56" s="10" t="s">
+      <c r="I56" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" ht="70" customHeight="1" spans="1:9">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="G57" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="I57" s="10" t="s">
+      <c r="I57" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="58" ht="70" customHeight="1" spans="1:9">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="F58" s="10" t="s">
+      <c r="F58" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="G58" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="H58" s="10" t="s">
+      <c r="H58" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="I58" s="10" t="s">
+      <c r="I58" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="59" ht="70" customHeight="1" spans="1:9">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="F59" s="10" t="s">
+      <c r="F59" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="G59" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="H59" s="10" t="s">
+      <c r="H59" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="I59" s="10" t="s">
+      <c r="I59" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="60" ht="70" customHeight="1" spans="1:9">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="F60" s="10" t="s">
+      <c r="F60" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="G60" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="H60" s="10" t="s">
+      <c r="H60" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="I60" s="10" t="s">
+      <c r="I60" s="15" t="s">
         <v>22</v>
       </c>
     </row>
